--- a/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
+++ b/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/pkasaie1_jh_edu/Documents/SHIELDR01/Simulation/code/jheem_analyses/applications/SHIELD/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23D90AD4-FCD4-3B45-9171-A86A250AF0D4}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B646EE-30FE-2949-818F-5DC08637FFE1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34560" windowHeight="19520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="76580" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="CA" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
+    <sheet name="CA" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$5:$H$59</definedName>
@@ -3750,6 +3751,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE604CA6-5D88-0144-B08A-91DBBAA3536C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1">
+        <f>2395*12</f>
+        <v>28740</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256FC72E-A572-7D4B-A75E-263A2A9F0674}">
   <dimension ref="B1:M48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
+++ b/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/pkasaie1_jh_edu/Documents/SHIELDR01/Simulation/code/jheem_analyses/applications/SHIELD/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88B646EE-30FE-2949-818F-5DC08637FFE1}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADEF3F69-C8C5-7A4B-B8DF-59FF261C779A}"/>
   <bookViews>
     <workbookView xWindow="76580" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3752,13 +3752,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE604CA6-5D88-0144-B08A-91DBBAA3536C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1">
         <f>2395*12</f>
         <v>28740</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6">
+      <c r="F32">
+        <f>2096695381/737690966</f>
+        <v>2.8422408266282062</v>
       </c>
     </row>
   </sheetData>

--- a/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
+++ b/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/pkasaie1_jh_edu/Documents/SHIELDR01/Simulation/code/jheem_analyses/applications/SHIELD/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADEF3F69-C8C5-7A4B-B8DF-59FF261C779A}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702B993E-90EC-F74B-B598-1B911A505FF1}"/>
   <bookViews>
-    <workbookView xWindow="76580" yWindow="600" windowWidth="38400" windowHeight="19520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="34560" yWindow="600" windowWidth="34560" windowHeight="19440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
-    <sheet name="CA" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
+    <sheet name="CA" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$5:$H$59</definedName>
@@ -3773,6 +3774,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360C4CA0-CBDB-7E4B-9B6E-528523E8BE4D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256FC72E-A572-7D4B-A75E-263A2A9F0674}">
   <dimension ref="B1:M48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
+++ b/applications/SHIELD/Documentation/PS Syphilis - Cases by Sex and Sex of Sex Partners (US 2015-2024).xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejohnshopkins-my.sharepoint.com/personal/pkasaie1_jh_edu/Documents/SHIELDR01/Simulation/code/jheem_analyses/applications/SHIELD/Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702B993E-90EC-F74B-B598-1B911A505FF1}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{A0F7102C-F699-B042-A64E-207DB11C90FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4086FCA9-99F0-2E47-BF35-586696D0510F}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="34560" yWindow="600" windowWidth="34560" windowHeight="19440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="600" windowWidth="34560" windowHeight="19440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
-    <sheet name="CA" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId5"/>
+    <sheet name="CA" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$5:$H$59</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
   <si>
     <t>STI</t>
   </si>
@@ -181,6 +182,84 @@
   </si>
   <si>
     <t>stdev</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>Effectiveness</t>
+  </si>
+  <si>
+    <t>Number of diabetes diagnosis averted per 1,000 persons receiving intervention</t>
+  </si>
+  <si>
+    <t>Black HET Women</t>
+  </si>
+  <si>
+    <t>White HET Women</t>
+  </si>
+  <si>
+    <t>Hispanic HET Women</t>
+  </si>
+  <si>
+    <t>Black HET Men</t>
+  </si>
+  <si>
+    <t>White HET Men</t>
+  </si>
+  <si>
+    <t>Hispanic HET Men</t>
+  </si>
+  <si>
+    <t>Black WWID</t>
+  </si>
+  <si>
+    <t>White WWID</t>
+  </si>
+  <si>
+    <t>Hispanic WWID</t>
+  </si>
+  <si>
+    <t>Black MWID</t>
+  </si>
+  <si>
+    <t>White MWID</t>
+  </si>
+  <si>
+    <t>Hispanic MWID</t>
+  </si>
+  <si>
+    <t>Black MSM</t>
+  </si>
+  <si>
+    <t>White MSM</t>
+  </si>
+  <si>
+    <t>Hispanic MSM</t>
+  </si>
+  <si>
+    <t>50%%</t>
+  </si>
+  <si>
+    <t>25%%</t>
+  </si>
+  <si>
+    <t>Number of diabetes diagnosis averted</t>
+  </si>
+  <si>
+    <t>Absolute Change from Baseline (75% effectiveness)</t>
+  </si>
+  <si>
+    <t>Relative Change from Baseline (75% effectiveness)</t>
+  </si>
+  <si>
+    <t>Absolute Change (75% effectiveness)</t>
+  </si>
+  <si>
+    <t>Relative Change (75% effectiveness)</t>
+  </si>
+  <si>
+    <t>75% (baseline)</t>
   </si>
 </sst>
 </file>
@@ -192,7 +271,7 @@
     <numFmt numFmtId="165" formatCode="#,##0&quot; &quot;"/>
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -311,8 +390,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,8 +442,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E2841"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E2841"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -523,6 +640,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -530,7 +803,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -659,19 +932,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2747,26 +3084,26 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="18" style="51" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:15">
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="M3" s="46" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="M3" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
     </row>
     <row r="4" spans="1:15">
       <c r="B4" s="45"/>
@@ -2774,7 +3111,7 @@
       <c r="D4" s="45"/>
       <c r="E4" s="45"/>
       <c r="F4" s="45"/>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="48" t="s">
         <v>36</v>
       </c>
       <c r="H4" s="45"/>
@@ -2802,7 +3139,7 @@
       <c r="F5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -2837,7 +3174,7 @@
       <c r="F6">
         <v>27</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6">
         <f>B6/SUM(B6:C6)</f>
         <v>0.81742976963290626</v>
       </c>
@@ -2869,7 +3206,7 @@
       <c r="F7">
         <v>41</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7">
         <f t="shared" ref="G7:G15" si="0">B7/SUM(B7:C7)</f>
         <v>0.80633890691290244</v>
       </c>
@@ -2901,7 +3238,7 @@
       <c r="F8">
         <v>37</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>0.79590737749057616</v>
       </c>
@@ -2933,7 +3270,7 @@
       <c r="F9">
         <v>34</v>
       </c>
-      <c r="G9" s="51">
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>0.77597617471872937</v>
       </c>
@@ -2965,7 +3302,7 @@
       <c r="F10">
         <v>97</v>
       </c>
-      <c r="G10" s="51">
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>0.71604986365407086</v>
       </c>
@@ -2997,7 +3334,7 @@
       <c r="F11">
         <v>108</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>0.69727191586790327</v>
       </c>
@@ -3029,7 +3366,7 @@
       <c r="F12">
         <v>153</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12">
         <f t="shared" si="0"/>
         <v>0.6313491151459435</v>
       </c>
@@ -3070,7 +3407,7 @@
       <c r="F13">
         <v>55</v>
       </c>
-      <c r="G13" s="51">
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>0.59958636813236221</v>
       </c>
@@ -3111,7 +3448,7 @@
       <c r="F14">
         <v>56</v>
       </c>
-      <c r="G14" s="51">
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>0.57463527851458884</v>
       </c>
@@ -3133,44 +3470,44 @@
         <v>0.54530916844349675</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="48" customFormat="1">
-      <c r="A15" s="48" t="s">
+    <row r="15" spans="1:15" s="47" customFormat="1">
+      <c r="A15" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="47">
         <v>12855</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="47">
         <v>9559</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="47">
         <v>7161</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="47">
         <v>11859</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="47">
         <v>62</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="47">
         <f t="shared" si="0"/>
         <v>0.57352547514946017</v>
       </c>
-      <c r="H15" s="48">
+      <c r="H15" s="47">
         <f t="shared" si="1"/>
         <v>0.2421301775147929</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="47">
         <f t="shared" si="2"/>
         <v>0.2857865818392134</v>
       </c>
-      <c r="M15" s="48">
+      <c r="M15" s="47">
         <v>2024</v>
       </c>
-      <c r="N15" s="48">
+      <c r="N15" s="47">
         <v>0.63421052631578945</v>
       </c>
-      <c r="O15" s="48">
+      <c r="O15" s="47">
         <v>0.50701754385964914</v>
       </c>
     </row>
@@ -3178,16 +3515,16 @@
       <c r="F17" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17">
         <f>AVERAGE(G6:G15)</f>
         <v>0.69880702452194432</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="46"/>
+      <c r="E23" s="49"/>
     </row>
     <row r="24" spans="1:7" ht="32">
       <c r="A24" s="6" t="s">
@@ -3295,7 +3632,7 @@
         <v>2.0105670103092783</v>
       </c>
       <c r="F30">
-        <f t="shared" ref="F30:F34" si="3">E30/D30</f>
+        <f t="shared" ref="F30:F32" si="3">E30/D30</f>
         <v>1.8076975763327243</v>
       </c>
     </row>
@@ -3390,7 +3727,7 @@
       <c r="B40">
         <v>14229</v>
       </c>
-      <c r="C40" s="47">
+      <c r="C40" s="46">
         <f>SUM(C6:D6)</f>
         <v>7318</v>
       </c>
@@ -3402,7 +3739,7 @@
       <c r="B41">
         <v>16155</v>
       </c>
-      <c r="C41" s="47">
+      <c r="C41" s="46">
         <f t="shared" ref="C41:C47" si="6">SUM(C7:D7)</f>
         <v>8569</v>
       </c>
@@ -3414,7 +3751,7 @@
       <c r="B42">
         <v>17736</v>
       </c>
-      <c r="C42" s="47">
+      <c r="C42" s="46">
         <f t="shared" si="6"/>
         <v>9149</v>
       </c>
@@ -3426,7 +3763,7 @@
       <c r="B43">
         <v>18760</v>
       </c>
-      <c r="C43" s="47">
+      <c r="C43" s="46">
         <f t="shared" si="6"/>
         <v>11274</v>
       </c>
@@ -3438,7 +3775,7 @@
       <c r="B44">
         <v>18381</v>
       </c>
-      <c r="C44" s="47">
+      <c r="C44" s="46">
         <f t="shared" si="6"/>
         <v>14021</v>
       </c>
@@ -3462,7 +3799,7 @@
       <c r="B45">
         <v>17968</v>
       </c>
-      <c r="C45" s="47">
+      <c r="C45" s="46">
         <f t="shared" si="6"/>
         <v>15678</v>
       </c>
@@ -3486,7 +3823,7 @@
       <c r="B46">
         <v>19229</v>
       </c>
-      <c r="C46" s="47">
+      <c r="C46" s="46">
         <f t="shared" si="6"/>
         <v>22120</v>
       </c>
@@ -3510,7 +3847,7 @@
       <c r="B47">
         <v>20004</v>
       </c>
-      <c r="C47" s="47">
+      <c r="C47" s="46">
         <f t="shared" si="6"/>
         <v>24305</v>
       </c>
@@ -3569,11 +3906,11 @@
       <c r="A54">
         <v>2015</v>
       </c>
-      <c r="B54" s="47">
+      <c r="B54" s="46">
         <f>B6+D6</f>
         <v>18369</v>
       </c>
-      <c r="C54" s="47">
+      <c r="C54" s="46">
         <f>C6</f>
         <v>3178</v>
       </c>
@@ -3582,11 +3919,11 @@
       <c r="A55">
         <v>2016</v>
       </c>
-      <c r="B55" s="47">
+      <c r="B55" s="46">
         <f t="shared" ref="B55:B61" si="10">B7+D7</f>
         <v>20844</v>
       </c>
-      <c r="C55" s="47">
+      <c r="C55" s="46">
         <f t="shared" ref="C55:C61" si="11">C7</f>
         <v>3880</v>
       </c>
@@ -3595,11 +3932,11 @@
       <c r="A56">
         <v>2017</v>
       </c>
-      <c r="B56" s="47">
+      <c r="B56" s="46">
         <f t="shared" si="10"/>
         <v>22337</v>
       </c>
-      <c r="C56" s="47">
+      <c r="C56" s="46">
         <f t="shared" si="11"/>
         <v>4548</v>
       </c>
@@ -3608,11 +3945,11 @@
       <c r="A57">
         <v>2018</v>
       </c>
-      <c r="B57" s="47">
+      <c r="B57" s="46">
         <f t="shared" si="10"/>
         <v>24618</v>
       </c>
-      <c r="C57" s="47">
+      <c r="C57" s="46">
         <f t="shared" si="11"/>
         <v>5416</v>
       </c>
@@ -3621,11 +3958,11 @@
       <c r="A58">
         <v>2019</v>
       </c>
-      <c r="B58" s="47">
+      <c r="B58" s="46">
         <f t="shared" si="10"/>
         <v>25113</v>
       </c>
-      <c r="C58" s="47">
+      <c r="C58" s="46">
         <f t="shared" si="11"/>
         <v>7289</v>
       </c>
@@ -3646,11 +3983,11 @@
       <c r="A59">
         <v>2020</v>
       </c>
-      <c r="B59" s="47">
+      <c r="B59" s="46">
         <f t="shared" si="10"/>
         <v>25845</v>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="46">
         <f t="shared" si="11"/>
         <v>7801</v>
       </c>
@@ -3671,11 +4008,11 @@
       <c r="A60">
         <v>2021</v>
       </c>
-      <c r="B60" s="47">
+      <c r="B60" s="46">
         <f t="shared" si="10"/>
         <v>30121</v>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="46">
         <f t="shared" si="11"/>
         <v>11228</v>
       </c>
@@ -3696,11 +4033,11 @@
       <c r="A61">
         <v>2022</v>
       </c>
-      <c r="B61" s="47">
+      <c r="B61" s="46">
         <f t="shared" si="10"/>
         <v>30950</v>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="46">
         <f t="shared" si="11"/>
         <v>13359</v>
       </c>
@@ -3752,6 +4089,747 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4363B46A-55FB-D04E-9130-A7173BB06898}">
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="21" width="9.6640625" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="20" customHeight="1" thickBot="1">
+      <c r="A1" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="53">
+        <v>100</v>
+      </c>
+      <c r="C1" s="53">
+        <v>100</v>
+      </c>
+      <c r="D1" s="53">
+        <v>100</v>
+      </c>
+      <c r="E1" s="53">
+        <v>100</v>
+      </c>
+      <c r="F1" s="54">
+        <v>100</v>
+      </c>
+      <c r="G1" s="53">
+        <v>100</v>
+      </c>
+      <c r="H1" s="53">
+        <v>100</v>
+      </c>
+      <c r="I1" s="54">
+        <v>100</v>
+      </c>
+      <c r="J1" s="53">
+        <v>100</v>
+      </c>
+      <c r="K1" s="53">
+        <v>100</v>
+      </c>
+      <c r="L1" s="53">
+        <v>100</v>
+      </c>
+      <c r="M1" s="53">
+        <v>100</v>
+      </c>
+      <c r="N1" s="53">
+        <v>100</v>
+      </c>
+      <c r="O1" s="53">
+        <v>100</v>
+      </c>
+      <c r="P1" s="54">
+        <v>100</v>
+      </c>
+      <c r="Q1" s="53">
+        <v>100</v>
+      </c>
+      <c r="R1" s="53">
+        <v>100</v>
+      </c>
+      <c r="S1" s="54">
+        <v>100</v>
+      </c>
+      <c r="T1" s="53">
+        <v>100</v>
+      </c>
+      <c r="U1" s="53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="20" customHeight="1" thickBot="1">
+      <c r="A2" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="56">
+        <v>100</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="59">
+        <v>100</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="59">
+        <v>100</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="56">
+        <v>100</v>
+      </c>
+      <c r="M2" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="59">
+        <v>100</v>
+      </c>
+      <c r="Q2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="S2" s="59">
+        <v>100</v>
+      </c>
+      <c r="T2" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="58" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A3" s="50"/>
+      <c r="B3" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="61"/>
+      <c r="K3" s="62"/>
+      <c r="L3" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="61"/>
+      <c r="U3" s="62"/>
+    </row>
+    <row r="4" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A4" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="63">
+        <v>35</v>
+      </c>
+      <c r="C4" s="63">
+        <v>26</v>
+      </c>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63">
+        <v>9</v>
+      </c>
+      <c r="G4" s="63"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="63">
+        <v>0.26</v>
+      </c>
+      <c r="J4" s="63"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="65">
+        <v>341</v>
+      </c>
+      <c r="M4" s="66">
+        <v>253</v>
+      </c>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="64"/>
+    </row>
+    <row r="5" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A5" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="67">
+        <v>26</v>
+      </c>
+      <c r="C5" s="67">
+        <v>19</v>
+      </c>
+      <c r="D5" s="67"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="67">
+        <v>7</v>
+      </c>
+      <c r="G5" s="67"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="67">
+        <v>0.27</v>
+      </c>
+      <c r="J5" s="67"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="69">
+        <v>67</v>
+      </c>
+      <c r="M5" s="70">
+        <v>49</v>
+      </c>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="68"/>
+    </row>
+    <row r="6" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A6" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="63">
+        <v>26</v>
+      </c>
+      <c r="C6" s="63">
+        <v>20</v>
+      </c>
+      <c r="D6" s="63"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="63">
+        <v>6</v>
+      </c>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="63">
+        <v>0.23</v>
+      </c>
+      <c r="J6" s="63"/>
+      <c r="K6" s="64"/>
+      <c r="L6" s="71">
+        <v>73</v>
+      </c>
+      <c r="M6" s="72">
+        <v>55</v>
+      </c>
+      <c r="N6" s="63"/>
+      <c r="O6" s="64"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="63"/>
+      <c r="U6" s="64"/>
+    </row>
+    <row r="7" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A7" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="67">
+        <v>28</v>
+      </c>
+      <c r="C7" s="67">
+        <v>21</v>
+      </c>
+      <c r="D7" s="67"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="67">
+        <v>7</v>
+      </c>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="67">
+        <v>0.25</v>
+      </c>
+      <c r="J7" s="67"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="69">
+        <v>178</v>
+      </c>
+      <c r="M7" s="70">
+        <v>133</v>
+      </c>
+      <c r="N7" s="67"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="68"/>
+    </row>
+    <row r="8" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A8" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="63">
+        <v>30</v>
+      </c>
+      <c r="C8" s="63">
+        <v>21</v>
+      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="63">
+        <v>9</v>
+      </c>
+      <c r="G8" s="63"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="63">
+        <v>0.3</v>
+      </c>
+      <c r="J8" s="63"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="71">
+        <v>44</v>
+      </c>
+      <c r="M8" s="72">
+        <v>32</v>
+      </c>
+      <c r="N8" s="63"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="64"/>
+    </row>
+    <row r="9" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A9" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="67">
+        <v>40</v>
+      </c>
+      <c r="C9" s="67">
+        <v>30</v>
+      </c>
+      <c r="D9" s="67"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="67">
+        <v>10</v>
+      </c>
+      <c r="G9" s="67"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="67">
+        <v>0.25</v>
+      </c>
+      <c r="J9" s="67"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="69">
+        <v>83</v>
+      </c>
+      <c r="M9" s="70">
+        <v>62</v>
+      </c>
+      <c r="N9" s="67"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="68"/>
+    </row>
+    <row r="10" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A10" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="63">
+        <v>29</v>
+      </c>
+      <c r="C10" s="63">
+        <v>23</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="63">
+        <v>6</v>
+      </c>
+      <c r="G10" s="63"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="63">
+        <v>0.21</v>
+      </c>
+      <c r="J10" s="63"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="71">
+        <v>33</v>
+      </c>
+      <c r="M10" s="72">
+        <v>25</v>
+      </c>
+      <c r="N10" s="63"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="64"/>
+      <c r="S10" s="63"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="64"/>
+    </row>
+    <row r="11" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A11" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="67">
+        <v>47</v>
+      </c>
+      <c r="C11" s="67">
+        <v>34</v>
+      </c>
+      <c r="D11" s="67"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="67">
+        <v>13</v>
+      </c>
+      <c r="G11" s="67"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="67">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J11" s="67"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="69">
+        <v>67</v>
+      </c>
+      <c r="M11" s="70">
+        <v>49</v>
+      </c>
+      <c r="N11" s="67"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="68"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="68"/>
+    </row>
+    <row r="12" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A12" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="63">
+        <v>43</v>
+      </c>
+      <c r="C12" s="63">
+        <v>32</v>
+      </c>
+      <c r="D12" s="63"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="63">
+        <v>11</v>
+      </c>
+      <c r="G12" s="63"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="63">
+        <v>0.26</v>
+      </c>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
+      <c r="L12" s="71">
+        <v>26</v>
+      </c>
+      <c r="M12" s="72">
+        <v>19</v>
+      </c>
+      <c r="N12" s="63"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="64"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="63"/>
+      <c r="U12" s="64"/>
+    </row>
+    <row r="13" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A13" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="67">
+        <v>29</v>
+      </c>
+      <c r="C13" s="67">
+        <v>21</v>
+      </c>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="67">
+        <v>8</v>
+      </c>
+      <c r="G13" s="67"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="67">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="69">
+        <v>78</v>
+      </c>
+      <c r="M13" s="70">
+        <v>54</v>
+      </c>
+      <c r="N13" s="67"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="68"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+      <c r="U13" s="68"/>
+    </row>
+    <row r="14" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A14" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="63">
+        <v>4</v>
+      </c>
+      <c r="C14" s="63">
+        <v>3</v>
+      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="63">
+        <v>1</v>
+      </c>
+      <c r="G14" s="63"/>
+      <c r="H14" s="64"/>
+      <c r="I14" s="63">
+        <v>0.25</v>
+      </c>
+      <c r="J14" s="63"/>
+      <c r="K14" s="64"/>
+      <c r="L14" s="71">
+        <v>17</v>
+      </c>
+      <c r="M14" s="72">
+        <v>13</v>
+      </c>
+      <c r="N14" s="63"/>
+      <c r="O14" s="64"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="63"/>
+      <c r="T14" s="63"/>
+      <c r="U14" s="64"/>
+    </row>
+    <row r="15" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A15" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="67">
+        <v>4</v>
+      </c>
+      <c r="C15" s="67">
+        <v>3</v>
+      </c>
+      <c r="D15" s="67"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67">
+        <v>1</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="67">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="67"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="69">
+        <v>9</v>
+      </c>
+      <c r="M15" s="70">
+        <v>7</v>
+      </c>
+      <c r="N15" s="67"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="68"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="68"/>
+    </row>
+    <row r="16" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A16" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="63">
+        <v>11</v>
+      </c>
+      <c r="C16" s="63">
+        <v>8</v>
+      </c>
+      <c r="D16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="63">
+        <v>3</v>
+      </c>
+      <c r="G16" s="63"/>
+      <c r="H16" s="64"/>
+      <c r="I16" s="63">
+        <v>0.27</v>
+      </c>
+      <c r="J16" s="63"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="71">
+        <v>379</v>
+      </c>
+      <c r="M16" s="72">
+        <v>283</v>
+      </c>
+      <c r="N16" s="63"/>
+      <c r="O16" s="64"/>
+      <c r="P16" s="63"/>
+      <c r="Q16" s="63"/>
+      <c r="R16" s="64"/>
+      <c r="S16" s="63"/>
+      <c r="T16" s="63"/>
+      <c r="U16" s="64"/>
+    </row>
+    <row r="17" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A17" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="67">
+        <v>8</v>
+      </c>
+      <c r="C17" s="67">
+        <v>6</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67">
+        <v>2</v>
+      </c>
+      <c r="G17" s="67"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="67">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="67"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="69">
+        <v>208</v>
+      </c>
+      <c r="M17" s="70">
+        <v>160</v>
+      </c>
+      <c r="N17" s="67"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="67"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="68"/>
+    </row>
+    <row r="18" spans="1:21" ht="20" customHeight="1" thickBot="1">
+      <c r="A18" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="63">
+        <v>6</v>
+      </c>
+      <c r="C18" s="63">
+        <v>4</v>
+      </c>
+      <c r="D18" s="63"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="63">
+        <v>2</v>
+      </c>
+      <c r="G18" s="63"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="63">
+        <v>0.33</v>
+      </c>
+      <c r="J18" s="63"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="71">
+        <v>163</v>
+      </c>
+      <c r="M18" s="72">
+        <v>125</v>
+      </c>
+      <c r="N18" s="63"/>
+      <c r="O18" s="64"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="63"/>
+      <c r="T18" s="63"/>
+      <c r="U18" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:U3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE604CA6-5D88-0144-B08A-91DBBAA3536C}">
   <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -3773,7 +4851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{360C4CA0-CBDB-7E4B-9B6E-528523E8BE4D}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
@@ -3782,7 +4860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256FC72E-A572-7D4B-A75E-263A2A9F0674}">
   <dimension ref="B1:M48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -4259,9 +5337,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4409,26 +5490,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9314C9C2-CF3A-4EA0-A3E9-3F9A67E25F7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A398BB-3F22-473A-B122-4323C2BAEF64}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="cf623074-13d1-44e3-9013-94496ccdf7fb"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4452,9 +5522,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79A398BB-3F22-473A-B122-4323C2BAEF64}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9314C9C2-CF3A-4EA0-A3E9-3F9A67E25F7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="cf623074-13d1-44e3-9013-94496ccdf7fb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>